--- a/data/fr/FR_Budget_Status.xlsx
+++ b/data/fr/FR_Budget_Status.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="OPEN LINE FR" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="48">
   <si>
     <t>Plan Head</t>
   </si>
@@ -163,9 +163,6 @@
     <t>SBA 2026-27</t>
   </si>
   <si>
-    <t>22.06.2026</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -187,7 +184,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  30.06.2026  (Fig.in Thousand) </t>
+      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  28.07.2026  (Fig.in Thousand) </t>
     </r>
     <r>
       <rPr>
@@ -223,7 +220,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Actual.  Expenditure of Demand 16 GSU as on  30.06.2026  (Fig.in Thousand)</t>
+      <t>Actual.  Expenditure of Demand 16 GSU as on  28.07.2026  (Fig.in Thousand)</t>
     </r>
     <r>
       <rPr>
@@ -3048,7 +3045,7 @@
   <sheetData>
     <row r="1" spans="1:244" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -3216,11 +3213,11 @@
         <v>146190</v>
       </c>
       <c r="D4" s="13">
-        <v>26053</v>
+        <v>48449</v>
       </c>
       <c r="E4" s="14">
         <f>D4-C4</f>
-        <v>-120137</v>
+        <v>-97741</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
@@ -3288,15 +3285,15 @@
       </c>
       <c r="Y4" s="13">
         <f t="shared" si="3"/>
-        <v>26747</v>
+        <v>49143</v>
       </c>
       <c r="Z4" s="14">
         <f>Y4-X4</f>
-        <v>-134156</v>
+        <v>-111760</v>
       </c>
       <c r="AA4" s="6">
         <f>Y4/X4*100</f>
-        <v>16.623058612953145</v>
+        <v>30.542003567366677</v>
       </c>
       <c r="AB4"/>
       <c r="AC4"/>
@@ -3383,11 +3380,11 @@
         <v>4107</v>
       </c>
       <c r="D5" s="6">
-        <v>2511</v>
+        <v>2818</v>
       </c>
       <c r="E5" s="14">
         <f t="shared" ref="E5:E21" si="4">D5-C5</f>
-        <v>-1596</v>
+        <v>-1289</v>
       </c>
       <c r="F5" s="5">
         <v>14120</v>
@@ -3455,15 +3452,15 @@
       </c>
       <c r="Y5" s="13">
         <f t="shared" si="3"/>
-        <v>3375</v>
+        <v>3682</v>
       </c>
       <c r="Z5" s="14">
         <f t="shared" ref="Z5:Z21" si="8">Y5-X5</f>
-        <v>-28852</v>
+        <v>-28545</v>
       </c>
       <c r="AA5" s="6">
         <f t="shared" ref="AA5:AA20" si="9">Y5/X5*100</f>
-        <v>10.472585099450772</v>
+        <v>11.425202469978588</v>
       </c>
     </row>
     <row r="6" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3517,11 +3514,11 @@
         <v>120318</v>
       </c>
       <c r="P6" s="8">
-        <v>45115</v>
+        <v>49669</v>
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="7"/>
-        <v>-75203</v>
+        <v>-70649</v>
       </c>
       <c r="R6" s="14">
         <v>0</v>
@@ -3549,15 +3546,15 @@
       </c>
       <c r="Y6" s="13">
         <f t="shared" si="3"/>
-        <v>45115</v>
+        <v>49669</v>
       </c>
       <c r="Z6" s="14">
         <f t="shared" si="8"/>
-        <v>-75203</v>
+        <v>-70649</v>
       </c>
       <c r="AA6" s="6">
         <f t="shared" si="9"/>
-        <v>37.496467693944382</v>
+        <v>41.281437523895008</v>
       </c>
     </row>
     <row r="7" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3611,11 +3608,11 @@
         <v>316420</v>
       </c>
       <c r="P7" s="8">
-        <v>194943</v>
+        <v>221758</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="7"/>
-        <v>-121477</v>
+        <v>-94662</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -3631,11 +3628,11 @@
         <v>191000</v>
       </c>
       <c r="V7" s="6">
-        <v>85138</v>
+        <v>92917</v>
       </c>
       <c r="W7" s="14">
         <f t="shared" si="2"/>
-        <v>-105862</v>
+        <v>-98083</v>
       </c>
       <c r="X7" s="12">
         <f t="shared" si="3"/>
@@ -3643,15 +3640,15 @@
       </c>
       <c r="Y7" s="13">
         <f t="shared" si="3"/>
-        <v>280081</v>
+        <v>314675</v>
       </c>
       <c r="Z7" s="14">
         <f t="shared" si="8"/>
-        <v>-227339</v>
+        <v>-192745</v>
       </c>
       <c r="AA7" s="6">
         <f t="shared" si="9"/>
-        <v>55.197075401048444</v>
+        <v>62.01470182491822</v>
       </c>
     </row>
     <row r="8" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3705,11 +3702,11 @@
         <v>2645397</v>
       </c>
       <c r="P8" s="8">
-        <v>2131498</v>
+        <v>2172711</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" si="7"/>
-        <v>-513899</v>
+        <v>-472686</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -3725,11 +3722,11 @@
         <v>317398</v>
       </c>
       <c r="V8" s="6">
-        <v>178422</v>
+        <v>183459</v>
       </c>
       <c r="W8" s="14">
         <f t="shared" si="2"/>
-        <v>-138976</v>
+        <v>-133939</v>
       </c>
       <c r="X8" s="12">
         <f t="shared" si="3"/>
@@ -3737,15 +3734,15 @@
       </c>
       <c r="Y8" s="13">
         <f t="shared" si="3"/>
-        <v>2309920</v>
+        <v>2356170</v>
       </c>
       <c r="Z8" s="14">
         <f t="shared" si="8"/>
-        <v>-652875</v>
+        <v>-606625</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="9"/>
-        <v>77.964219596698399</v>
+        <v>79.525245587359223</v>
       </c>
     </row>
     <row r="9" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3799,11 +3796,11 @@
         <v>35380</v>
       </c>
       <c r="P9" s="15">
-        <v>14445</v>
+        <v>19188</v>
       </c>
       <c r="Q9" s="14">
         <f t="shared" si="7"/>
-        <v>-20935</v>
+        <v>-16192</v>
       </c>
       <c r="R9" s="14">
         <v>0</v>
@@ -3819,11 +3816,11 @@
         <v>96867</v>
       </c>
       <c r="V9" s="13">
-        <v>103026</v>
+        <v>116765</v>
       </c>
       <c r="W9" s="14">
         <f t="shared" si="2"/>
-        <v>6159</v>
+        <v>19898</v>
       </c>
       <c r="X9" s="12">
         <f t="shared" si="3"/>
@@ -3831,15 +3828,15 @@
       </c>
       <c r="Y9" s="13">
         <f t="shared" si="3"/>
-        <v>117471</v>
+        <v>135953</v>
       </c>
       <c r="Z9" s="14">
         <f t="shared" si="8"/>
-        <v>-14796</v>
+        <v>3686</v>
       </c>
       <c r="AA9" s="6">
         <f t="shared" si="9"/>
-        <v>88.813536256209034</v>
+        <v>102.78678733168516</v>
       </c>
       <c r="AB9"/>
       <c r="AC9"/>
@@ -4070,11 +4067,11 @@
         <v>159700</v>
       </c>
       <c r="D10" s="13">
-        <v>7634</v>
+        <v>8146</v>
       </c>
       <c r="E10" s="14">
         <f t="shared" si="4"/>
-        <v>-152066</v>
+        <v>-151554</v>
       </c>
       <c r="F10" s="12">
         <v>0</v>
@@ -4130,11 +4127,11 @@
         <v>363143</v>
       </c>
       <c r="V10" s="13">
-        <v>76152</v>
+        <v>109527</v>
       </c>
       <c r="W10" s="14">
         <f t="shared" si="2"/>
-        <v>-286991</v>
+        <v>-253616</v>
       </c>
       <c r="X10" s="12">
         <f t="shared" si="3"/>
@@ -4142,15 +4139,15 @@
       </c>
       <c r="Y10" s="13">
         <f t="shared" si="3"/>
-        <v>83786</v>
+        <v>117673</v>
       </c>
       <c r="Z10" s="14">
         <f t="shared" si="8"/>
-        <v>-439057</v>
+        <v>-405170</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="9"/>
-        <v>16.025078273975172</v>
+        <v>22.506373806286017</v>
       </c>
       <c r="AB10"/>
       <c r="AC10"/>
@@ -4381,11 +4378,11 @@
         <v>174056</v>
       </c>
       <c r="D11" s="6">
-        <v>65941</v>
+        <v>70459</v>
       </c>
       <c r="E11" s="14">
         <f t="shared" si="4"/>
-        <v>-108115</v>
+        <v>-103597</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -4441,11 +4438,11 @@
         <v>107957</v>
       </c>
       <c r="V11" s="6">
-        <v>11777</v>
+        <v>11903</v>
       </c>
       <c r="W11" s="14">
         <f t="shared" si="2"/>
-        <v>-96180</v>
+        <v>-96054</v>
       </c>
       <c r="X11" s="12">
         <f t="shared" si="3"/>
@@ -4453,15 +4450,15 @@
       </c>
       <c r="Y11" s="13">
         <f t="shared" si="3"/>
-        <v>77718</v>
+        <v>82362</v>
       </c>
       <c r="Z11" s="14">
         <f t="shared" si="8"/>
-        <v>-230125</v>
+        <v>-225481</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="9"/>
-        <v>25.245985778464998</v>
+        <v>26.754546960626037</v>
       </c>
     </row>
     <row r="12" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4569,11 +4566,11 @@
         <v>10884</v>
       </c>
       <c r="D13" s="6">
-        <v>282</v>
+        <v>1983</v>
       </c>
       <c r="E13" s="14">
         <f t="shared" si="4"/>
-        <v>-10602</v>
+        <v>-8901</v>
       </c>
       <c r="F13" s="5">
         <v>1</v>
@@ -4629,11 +4626,11 @@
         <v>2000</v>
       </c>
       <c r="V13" s="6">
-        <v>1637</v>
+        <v>1646</v>
       </c>
       <c r="W13" s="14">
         <f t="shared" si="2"/>
-        <v>-363</v>
+        <v>-354</v>
       </c>
       <c r="X13" s="12">
         <f t="shared" si="3"/>
@@ -4641,15 +4638,15 @@
       </c>
       <c r="Y13" s="13">
         <f t="shared" si="3"/>
-        <v>1919</v>
+        <v>3629</v>
       </c>
       <c r="Z13" s="14">
         <f t="shared" si="8"/>
-        <v>-11275</v>
+        <v>-9565</v>
       </c>
       <c r="AA13" s="6">
         <f t="shared" si="9"/>
-        <v>14.544489919660453</v>
+        <v>27.50492648173412</v>
       </c>
     </row>
     <row r="14" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4663,11 +4660,11 @@
         <v>35702</v>
       </c>
       <c r="D14" s="6">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="4"/>
-        <v>-33276</v>
+        <v>-33275</v>
       </c>
       <c r="F14" s="5">
         <v>2000</v>
@@ -4735,15 +4732,15 @@
       </c>
       <c r="Y14" s="13">
         <f t="shared" si="3"/>
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="Z14" s="14">
         <f t="shared" si="8"/>
-        <v>-51276</v>
+        <v>-51275</v>
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="9"/>
-        <v>4.517522624855685</v>
+        <v>4.5193847528956086</v>
       </c>
     </row>
     <row r="15" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4757,11 +4754,11 @@
         <v>62500</v>
       </c>
       <c r="D15" s="6">
-        <v>18119</v>
+        <v>31212</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="4"/>
-        <v>-44381</v>
+        <v>-31288</v>
       </c>
       <c r="F15" s="5">
         <v>12000</v>
@@ -4829,15 +4826,15 @@
       </c>
       <c r="Y15" s="13">
         <f t="shared" si="3"/>
-        <v>22047</v>
+        <v>35140</v>
       </c>
       <c r="Z15" s="14">
         <f t="shared" si="8"/>
-        <v>-75453</v>
+        <v>-62360</v>
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="9"/>
-        <v>22.612307692307692</v>
+        <v>36.041025641025641</v>
       </c>
     </row>
     <row r="16" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4851,11 +4848,11 @@
         <v>285610</v>
       </c>
       <c r="D16" s="13">
-        <v>120402</v>
+        <v>109952</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="4"/>
-        <v>-165208</v>
+        <v>-175658</v>
       </c>
       <c r="F16" s="12">
         <v>0</v>
@@ -4923,15 +4920,15 @@
       </c>
       <c r="Y16" s="13">
         <f t="shared" si="3"/>
-        <v>125504</v>
+        <v>115054</v>
       </c>
       <c r="Z16" s="14">
         <f t="shared" si="8"/>
-        <v>-185408</v>
+        <v>-195858</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="9"/>
-        <v>40.366405928365587</v>
+        <v>37.005326265953066</v>
       </c>
       <c r="AB16"/>
       <c r="AC16"/>
@@ -5130,11 +5127,11 @@
         <v>69550</v>
       </c>
       <c r="D18" s="13">
-        <v>19043</v>
+        <v>21544</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="4"/>
-        <v>-50507</v>
+        <v>-48006</v>
       </c>
       <c r="F18" s="12">
         <v>12111</v>
@@ -5150,11 +5147,11 @@
         <v>62003</v>
       </c>
       <c r="J18" s="13">
-        <v>6208</v>
+        <v>6804</v>
       </c>
       <c r="K18" s="14">
         <f t="shared" si="5"/>
-        <v>-55795</v>
+        <v>-55199</v>
       </c>
       <c r="L18" s="14">
         <v>0</v>
@@ -5190,11 +5187,11 @@
         <v>172069</v>
       </c>
       <c r="V18" s="29">
-        <v>38247</v>
+        <v>38637</v>
       </c>
       <c r="W18" s="14">
         <f t="shared" si="2"/>
-        <v>-133822</v>
+        <v>-133432</v>
       </c>
       <c r="X18" s="12">
         <f t="shared" si="3"/>
@@ -5202,15 +5199,15 @@
       </c>
       <c r="Y18" s="13">
         <f t="shared" si="3"/>
-        <v>71352</v>
+        <v>74839</v>
       </c>
       <c r="Z18" s="14">
         <f t="shared" si="8"/>
-        <v>-244381</v>
+        <v>-240894</v>
       </c>
       <c r="AA18" s="6">
         <f>Y18/X18*100</f>
-        <v>22.598841426141707</v>
+        <v>23.703255598876265</v>
       </c>
       <c r="AB18"/>
       <c r="AC18"/>
@@ -6859,11 +6856,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>262411</v>
+        <v>296990</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="4"/>
-        <v>-755942</v>
+        <v>-721363</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -6883,11 +6880,11 @@
       </c>
       <c r="J21" s="1">
         <f>SUM(J4:J20)</f>
-        <v>8107</v>
+        <v>8703</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" si="5"/>
-        <v>-122485</v>
+        <v>-121889</v>
       </c>
       <c r="L21" s="2">
         <f>SUM(L4:L20)</f>
@@ -6907,11 +6904,11 @@
       </c>
       <c r="P21" s="1">
         <f>SUM(P4:P20)</f>
-        <v>2386001</v>
+        <v>2463326</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="7"/>
-        <v>-731514</v>
+        <v>-654189</v>
       </c>
       <c r="R21" s="1">
         <f>SUM(R4:R20)</f>
@@ -6931,11 +6928,11 @@
       </c>
       <c r="V21" s="1">
         <f>SUM(V4:V20)</f>
-        <v>498296</v>
+        <v>558751</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="2"/>
-        <v>-802713</v>
+        <v>-742258</v>
       </c>
       <c r="X21" s="12">
         <f t="shared" si="13"/>
@@ -6943,18 +6940,15 @@
       </c>
       <c r="Y21" s="13">
         <f t="shared" si="13"/>
-        <v>3167461</v>
+        <v>3340416</v>
       </c>
       <c r="Z21" s="14">
         <f t="shared" si="8"/>
-        <v>-2440240</v>
+        <v>-2267285</v>
       </c>
       <c r="AA21" s="6">
         <f>Y21/X21*100</f>
-        <v>56.484127809239467</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>46</v>
+        <v>59.568368570292883</v>
       </c>
     </row>
     <row r="22" spans="1:1476" x14ac:dyDescent="0.25">
@@ -7854,7 +7848,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -8373,11 +8367,11 @@
         <v>1</v>
       </c>
       <c r="V7" s="6">
-        <v>0.69799999999999995</v>
+        <v>127</v>
       </c>
       <c r="W7" s="7">
         <f t="shared" si="10"/>
-        <v>-0.30200000000000005</v>
+        <v>126</v>
       </c>
       <c r="X7" s="5">
         <f t="shared" si="0"/>
@@ -8385,15 +8379,15 @@
       </c>
       <c r="Y7" s="6">
         <f t="shared" si="7"/>
-        <v>0.69799999999999995</v>
+        <v>127</v>
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="8"/>
-        <v>-0.30200000000000005</v>
+        <v>126</v>
       </c>
       <c r="AA7" s="6">
         <f t="shared" ref="AA7:AA21" si="11">Y7/X7*100</f>
-        <v>69.8</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="8" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -8966,11 +8960,11 @@
         <v>5001</v>
       </c>
       <c r="D14" s="6">
-        <v>0</v>
+        <v>2048</v>
       </c>
       <c r="E14" s="7">
         <f t="shared" si="2"/>
-        <v>-5001</v>
+        <v>-2953</v>
       </c>
       <c r="F14" s="5">
         <v>0</v>
@@ -9038,15 +9032,15 @@
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2048</v>
       </c>
       <c r="Z14" s="7">
         <f t="shared" si="8"/>
-        <v>-5001</v>
+        <v>-2953</v>
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>40.951809638072383</v>
       </c>
     </row>
     <row r="15" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -9151,11 +9145,11 @@
         <v>446600</v>
       </c>
       <c r="D16" s="6">
-        <v>198329</v>
+        <v>239160</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" si="2"/>
-        <v>-248271</v>
+        <v>-207440</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -9223,15 +9217,15 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="7"/>
-        <v>198329</v>
+        <v>239160</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="8"/>
-        <v>-248271</v>
+        <v>-207440</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="11"/>
-        <v>44.408643081056873</v>
+        <v>53.551276309896998</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -9618,11 +9612,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>198329</v>
+        <v>241208</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" ref="E21" si="20">D21-C21</f>
-        <v>-253272</v>
+        <v>-210393</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -9689,11 +9683,11 @@
       </c>
       <c r="V21" s="1">
         <f>SUM(V4:V20)</f>
-        <v>0.69799999999999995</v>
+        <v>127</v>
       </c>
       <c r="W21" s="7">
         <f>V21-U21</f>
-        <v>-0.30200000000000005</v>
+        <v>126</v>
       </c>
       <c r="X21" s="5">
         <f t="shared" si="19"/>
@@ -9701,15 +9695,15 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="7"/>
-        <v>198329.698</v>
+        <v>241335</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="8"/>
-        <v>-253273.302</v>
+        <v>-210268</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="11"/>
-        <v>43.916824733228076</v>
+        <v>53.439636140592519</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">

--- a/data/fr/FR_Budget_Status.xlsx
+++ b/data/fr/FR_Budget_Status.xlsx
@@ -184,7 +184,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  28.07.2026  (Fig.in Thousand) </t>
+      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  31.07.2026  (Fig.in Thousand) </t>
     </r>
     <r>
       <rPr>
@@ -220,7 +220,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Actual.  Expenditure of Demand 16 GSU as on  28.07.2026  (Fig.in Thousand)</t>
+      <t>Actual.  Expenditure of Demand 16 GSU as on  31.07.2026  (Fig.in Thousand)</t>
     </r>
     <r>
       <rPr>
@@ -3380,11 +3380,11 @@
         <v>4107</v>
       </c>
       <c r="D5" s="6">
-        <v>2818</v>
+        <v>2877</v>
       </c>
       <c r="E5" s="14">
         <f t="shared" ref="E5:E21" si="4">D5-C5</f>
-        <v>-1289</v>
+        <v>-1230</v>
       </c>
       <c r="F5" s="5">
         <v>14120</v>
@@ -3400,11 +3400,11 @@
         <v>14000</v>
       </c>
       <c r="J5" s="6">
-        <v>0</v>
+        <v>1548</v>
       </c>
       <c r="K5" s="14">
         <f t="shared" ref="K5:K21" si="5">J5-I5</f>
-        <v>-14000</v>
+        <v>-12452</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -3452,15 +3452,15 @@
       </c>
       <c r="Y5" s="13">
         <f t="shared" si="3"/>
-        <v>3682</v>
+        <v>5289</v>
       </c>
       <c r="Z5" s="14">
         <f t="shared" ref="Z5:Z21" si="8">Y5-X5</f>
-        <v>-28545</v>
+        <v>-26938</v>
       </c>
       <c r="AA5" s="6">
         <f t="shared" ref="AA5:AA20" si="9">Y5/X5*100</f>
-        <v>11.425202469978588</v>
+        <v>16.411704471405962</v>
       </c>
     </row>
     <row r="6" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,11 +3608,11 @@
         <v>316420</v>
       </c>
       <c r="P7" s="8">
-        <v>221758</v>
+        <v>227359</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="7"/>
-        <v>-94662</v>
+        <v>-89061</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -3640,15 +3640,15 @@
       </c>
       <c r="Y7" s="13">
         <f t="shared" si="3"/>
-        <v>314675</v>
+        <v>320276</v>
       </c>
       <c r="Z7" s="14">
         <f t="shared" si="8"/>
-        <v>-192745</v>
+        <v>-187144</v>
       </c>
       <c r="AA7" s="6">
         <f t="shared" si="9"/>
-        <v>62.01470182491822</v>
+        <v>63.118521146190531</v>
       </c>
     </row>
     <row r="8" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3702,11 +3702,11 @@
         <v>2645397</v>
       </c>
       <c r="P8" s="8">
-        <v>2172711</v>
+        <v>2807034</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" si="7"/>
-        <v>-472686</v>
+        <v>161637</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -3722,11 +3722,11 @@
         <v>317398</v>
       </c>
       <c r="V8" s="6">
-        <v>183459</v>
+        <v>213584</v>
       </c>
       <c r="W8" s="14">
         <f t="shared" si="2"/>
-        <v>-133939</v>
+        <v>-103814</v>
       </c>
       <c r="X8" s="12">
         <f t="shared" si="3"/>
@@ -3734,15 +3734,15 @@
       </c>
       <c r="Y8" s="13">
         <f t="shared" si="3"/>
-        <v>2356170</v>
+        <v>3020618</v>
       </c>
       <c r="Z8" s="14">
         <f t="shared" si="8"/>
-        <v>-606625</v>
+        <v>57823</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="9"/>
-        <v>79.525245587359223</v>
+        <v>101.95163688341582</v>
       </c>
     </row>
     <row r="9" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4127,11 +4127,11 @@
         <v>363143</v>
       </c>
       <c r="V10" s="13">
-        <v>109527</v>
+        <v>109571</v>
       </c>
       <c r="W10" s="14">
         <f t="shared" si="2"/>
-        <v>-253616</v>
+        <v>-253572</v>
       </c>
       <c r="X10" s="12">
         <f t="shared" si="3"/>
@@ -4139,15 +4139,15 @@
       </c>
       <c r="Y10" s="13">
         <f t="shared" si="3"/>
-        <v>117673</v>
+        <v>117717</v>
       </c>
       <c r="Z10" s="14">
         <f t="shared" si="8"/>
-        <v>-405170</v>
+        <v>-405126</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="9"/>
-        <v>22.506373806286017</v>
+        <v>22.514789334465604</v>
       </c>
       <c r="AB10"/>
       <c r="AC10"/>
@@ -4438,11 +4438,11 @@
         <v>107957</v>
       </c>
       <c r="V11" s="6">
-        <v>11903</v>
+        <v>14300</v>
       </c>
       <c r="W11" s="14">
         <f t="shared" si="2"/>
-        <v>-96054</v>
+        <v>-93657</v>
       </c>
       <c r="X11" s="12">
         <f t="shared" si="3"/>
@@ -4450,15 +4450,15 @@
       </c>
       <c r="Y11" s="13">
         <f t="shared" si="3"/>
-        <v>82362</v>
+        <v>84759</v>
       </c>
       <c r="Z11" s="14">
         <f t="shared" si="8"/>
-        <v>-225481</v>
+        <v>-223084</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="9"/>
-        <v>26.754546960626037</v>
+        <v>27.533190619893904</v>
       </c>
     </row>
     <row r="12" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4660,11 +4660,11 @@
         <v>35702</v>
       </c>
       <c r="D14" s="6">
-        <v>2427</v>
+        <v>4327</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="4"/>
-        <v>-33275</v>
+        <v>-31375</v>
       </c>
       <c r="F14" s="5">
         <v>2000</v>
@@ -4732,15 +4732,15 @@
       </c>
       <c r="Y14" s="13">
         <f t="shared" si="3"/>
-        <v>2427</v>
+        <v>4327</v>
       </c>
       <c r="Z14" s="14">
         <f t="shared" si="8"/>
-        <v>-51275</v>
+        <v>-49375</v>
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="9"/>
-        <v>4.5193847528956086</v>
+        <v>8.0574280287512572</v>
       </c>
     </row>
     <row r="15" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4848,11 +4848,11 @@
         <v>285610</v>
       </c>
       <c r="D16" s="13">
-        <v>109952</v>
+        <v>111485</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="4"/>
-        <v>-175658</v>
+        <v>-174125</v>
       </c>
       <c r="F16" s="12">
         <v>0</v>
@@ -4920,15 +4920,15 @@
       </c>
       <c r="Y16" s="13">
         <f t="shared" si="3"/>
-        <v>115054</v>
+        <v>116587</v>
       </c>
       <c r="Z16" s="14">
         <f t="shared" si="8"/>
-        <v>-195858</v>
+        <v>-194325</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="9"/>
-        <v>37.005326265953066</v>
+        <v>37.49839182791272</v>
       </c>
       <c r="AB16"/>
       <c r="AC16"/>
@@ -5127,21 +5127,21 @@
         <v>69550</v>
       </c>
       <c r="D18" s="13">
-        <v>21544</v>
+        <v>22945</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="4"/>
-        <v>-48006</v>
+        <v>-46605</v>
       </c>
       <c r="F18" s="12">
         <v>12111</v>
       </c>
       <c r="G18" s="13">
-        <v>7854</v>
+        <v>9239</v>
       </c>
       <c r="H18" s="14">
         <f t="shared" si="0"/>
-        <v>-4257</v>
+        <v>-2872</v>
       </c>
       <c r="I18" s="12">
         <v>62003</v>
@@ -5187,11 +5187,11 @@
         <v>172069</v>
       </c>
       <c r="V18" s="29">
-        <v>38637</v>
+        <v>41521</v>
       </c>
       <c r="W18" s="14">
         <f t="shared" si="2"/>
-        <v>-133432</v>
+        <v>-130548</v>
       </c>
       <c r="X18" s="12">
         <f t="shared" si="3"/>
@@ -5199,15 +5199,15 @@
       </c>
       <c r="Y18" s="13">
         <f t="shared" si="3"/>
-        <v>74839</v>
+        <v>80509</v>
       </c>
       <c r="Z18" s="14">
         <f t="shared" si="8"/>
-        <v>-240894</v>
+        <v>-235224</v>
       </c>
       <c r="AA18" s="6">
         <f>Y18/X18*100</f>
-        <v>23.703255598876265</v>
+        <v>25.49907675155907</v>
       </c>
       <c r="AB18"/>
       <c r="AC18"/>
@@ -6856,11 +6856,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>296990</v>
+        <v>301883</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="4"/>
-        <v>-721363</v>
+        <v>-716470</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -6868,11 +6868,11 @@
       </c>
       <c r="G21" s="1">
         <f>SUM(G4:G20)</f>
-        <v>12646</v>
+        <v>14031</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" si="0"/>
-        <v>-27586</v>
+        <v>-26201</v>
       </c>
       <c r="I21" s="2">
         <f>SUM(I4:I20)</f>
@@ -6880,11 +6880,11 @@
       </c>
       <c r="J21" s="1">
         <f>SUM(J4:J20)</f>
-        <v>8703</v>
+        <v>10251</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" si="5"/>
-        <v>-121889</v>
+        <v>-120341</v>
       </c>
       <c r="L21" s="2">
         <f>SUM(L4:L20)</f>
@@ -6904,11 +6904,11 @@
       </c>
       <c r="P21" s="1">
         <f>SUM(P4:P20)</f>
-        <v>2463326</v>
+        <v>3103250</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="7"/>
-        <v>-654189</v>
+        <v>-14265</v>
       </c>
       <c r="R21" s="1">
         <f>SUM(R4:R20)</f>
@@ -6928,11 +6928,11 @@
       </c>
       <c r="V21" s="1">
         <f>SUM(V4:V20)</f>
-        <v>558751</v>
+        <v>594201</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="2"/>
-        <v>-742258</v>
+        <v>-706808</v>
       </c>
       <c r="X21" s="12">
         <f t="shared" si="13"/>
@@ -6940,15 +6940,15 @@
       </c>
       <c r="Y21" s="13">
         <f t="shared" si="13"/>
-        <v>3340416</v>
+        <v>4023616</v>
       </c>
       <c r="Z21" s="14">
         <f t="shared" si="8"/>
-        <v>-2267285</v>
+        <v>-1584085</v>
       </c>
       <c r="AA21" s="6">
         <f>Y21/X21*100</f>
-        <v>59.568368570292883</v>
+        <v>71.751614431653906</v>
       </c>
     </row>
     <row r="22" spans="1:1476" x14ac:dyDescent="0.25">
@@ -9145,11 +9145,11 @@
         <v>446600</v>
       </c>
       <c r="D16" s="6">
-        <v>239160</v>
+        <v>244669</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" si="2"/>
-        <v>-207440</v>
+        <v>-201931</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -9217,15 +9217,15 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="7"/>
-        <v>239160</v>
+        <v>244669</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="8"/>
-        <v>-207440</v>
+        <v>-201931</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="11"/>
-        <v>53.551276309896998</v>
+        <v>54.784818629646217</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -9612,11 +9612,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>241208</v>
+        <v>246717</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" ref="E21" si="20">D21-C21</f>
-        <v>-210393</v>
+        <v>-204884</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -9695,15 +9695,15 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="7"/>
-        <v>241335</v>
+        <v>246844</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="8"/>
-        <v>-210268</v>
+        <v>-204759</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="11"/>
-        <v>53.439636140592519</v>
+        <v>54.659512890746967</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">

--- a/data/fr/FR_Budget_Status.xlsx
+++ b/data/fr/FR_Budget_Status.xlsx
@@ -172,6 +172,42 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">                                                                                                                                                      </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Actual.  Expenditure of Demand 16 GSU as on  17.08.2026  (Fig.in Thousand)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                                                                                             </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">                                                                                                              </t>
     </r>
     <r>
@@ -184,7 +220,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  31.07.2026  (Fig.in Thousand) </t>
+      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  17.08.2026  (Fig.in Thousand) </t>
     </r>
     <r>
       <rPr>
@@ -196,42 +232,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">                                                                                                                                       </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                                                                      </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Actual.  Expenditure of Demand 16 GSU as on  31.07.2026  (Fig.in Thousand)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">                                                                                                             </t>
     </r>
   </si>
 </sst>
@@ -3045,7 +3045,7 @@
   <sheetData>
     <row r="1" spans="1:244" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -3213,11 +3213,11 @@
         <v>146190</v>
       </c>
       <c r="D4" s="13">
-        <v>48449</v>
+        <v>76470</v>
       </c>
       <c r="E4" s="14">
         <f>D4-C4</f>
-        <v>-97741</v>
+        <v>-69720</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
@@ -3285,15 +3285,15 @@
       </c>
       <c r="Y4" s="13">
         <f t="shared" si="3"/>
-        <v>49143</v>
+        <v>77164</v>
       </c>
       <c r="Z4" s="14">
         <f>Y4-X4</f>
-        <v>-111760</v>
+        <v>-83739</v>
       </c>
       <c r="AA4" s="6">
         <f>Y4/X4*100</f>
-        <v>30.542003567366677</v>
+        <v>47.956843564134914</v>
       </c>
       <c r="AB4"/>
       <c r="AC4"/>
@@ -3380,11 +3380,11 @@
         <v>4107</v>
       </c>
       <c r="D5" s="6">
-        <v>2877</v>
+        <v>5001</v>
       </c>
       <c r="E5" s="14">
         <f t="shared" ref="E5:E21" si="4">D5-C5</f>
-        <v>-1230</v>
+        <v>894</v>
       </c>
       <c r="F5" s="5">
         <v>14120</v>
@@ -3400,11 +3400,11 @@
         <v>14000</v>
       </c>
       <c r="J5" s="6">
-        <v>1548</v>
+        <v>2587</v>
       </c>
       <c r="K5" s="14">
         <f t="shared" ref="K5:K21" si="5">J5-I5</f>
-        <v>-12452</v>
+        <v>-11413</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -3452,15 +3452,15 @@
       </c>
       <c r="Y5" s="13">
         <f t="shared" si="3"/>
-        <v>5289</v>
+        <v>8452</v>
       </c>
       <c r="Z5" s="14">
         <f t="shared" ref="Z5:Z21" si="8">Y5-X5</f>
-        <v>-26938</v>
+        <v>-23775</v>
       </c>
       <c r="AA5" s="6">
         <f t="shared" ref="AA5:AA20" si="9">Y5/X5*100</f>
-        <v>16.411704471405962</v>
+        <v>26.226456077202347</v>
       </c>
     </row>
     <row r="6" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3514,11 +3514,11 @@
         <v>120318</v>
       </c>
       <c r="P6" s="8">
-        <v>49669</v>
+        <v>55924</v>
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="7"/>
-        <v>-70649</v>
+        <v>-64394</v>
       </c>
       <c r="R6" s="14">
         <v>0</v>
@@ -3546,15 +3546,15 @@
       </c>
       <c r="Y6" s="13">
         <f t="shared" si="3"/>
-        <v>49669</v>
+        <v>55924</v>
       </c>
       <c r="Z6" s="14">
         <f t="shared" si="8"/>
-        <v>-70649</v>
+        <v>-64394</v>
       </c>
       <c r="AA6" s="6">
         <f t="shared" si="9"/>
-        <v>41.281437523895008</v>
+        <v>46.480160906929967</v>
       </c>
     </row>
     <row r="7" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,11 +3608,11 @@
         <v>316420</v>
       </c>
       <c r="P7" s="8">
-        <v>227359</v>
+        <v>230344</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="7"/>
-        <v>-89061</v>
+        <v>-86076</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -3628,11 +3628,11 @@
         <v>191000</v>
       </c>
       <c r="V7" s="6">
-        <v>92917</v>
+        <v>97525</v>
       </c>
       <c r="W7" s="14">
         <f t="shared" si="2"/>
-        <v>-98083</v>
+        <v>-93475</v>
       </c>
       <c r="X7" s="12">
         <f t="shared" si="3"/>
@@ -3640,15 +3640,15 @@
       </c>
       <c r="Y7" s="13">
         <f t="shared" si="3"/>
-        <v>320276</v>
+        <v>327869</v>
       </c>
       <c r="Z7" s="14">
         <f t="shared" si="8"/>
-        <v>-187144</v>
+        <v>-179551</v>
       </c>
       <c r="AA7" s="6">
         <f t="shared" si="9"/>
-        <v>63.118521146190531</v>
+        <v>64.614914666351339</v>
       </c>
     </row>
     <row r="8" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3702,11 +3702,11 @@
         <v>2645397</v>
       </c>
       <c r="P8" s="8">
-        <v>2807034</v>
+        <v>2837402</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" si="7"/>
-        <v>161637</v>
+        <v>192005</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -3722,11 +3722,11 @@
         <v>317398</v>
       </c>
       <c r="V8" s="6">
-        <v>213584</v>
+        <v>232941</v>
       </c>
       <c r="W8" s="14">
         <f t="shared" si="2"/>
-        <v>-103814</v>
+        <v>-84457</v>
       </c>
       <c r="X8" s="12">
         <f t="shared" si="3"/>
@@ -3734,15 +3734,15 @@
       </c>
       <c r="Y8" s="13">
         <f t="shared" si="3"/>
-        <v>3020618</v>
+        <v>3070343</v>
       </c>
       <c r="Z8" s="14">
         <f t="shared" si="8"/>
-        <v>57823</v>
+        <v>107548</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="9"/>
-        <v>101.95163688341582</v>
+        <v>103.62995077283443</v>
       </c>
     </row>
     <row r="9" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3816,11 +3816,11 @@
         <v>96867</v>
       </c>
       <c r="V9" s="13">
-        <v>116765</v>
+        <v>123322</v>
       </c>
       <c r="W9" s="14">
         <f t="shared" si="2"/>
-        <v>19898</v>
+        <v>26455</v>
       </c>
       <c r="X9" s="12">
         <f t="shared" si="3"/>
@@ -3828,15 +3828,15 @@
       </c>
       <c r="Y9" s="13">
         <f t="shared" si="3"/>
-        <v>135953</v>
+        <v>142510</v>
       </c>
       <c r="Z9" s="14">
         <f t="shared" si="8"/>
-        <v>3686</v>
+        <v>10243</v>
       </c>
       <c r="AA9" s="6">
         <f t="shared" si="9"/>
-        <v>102.78678733168516</v>
+        <v>107.74418411243923</v>
       </c>
       <c r="AB9"/>
       <c r="AC9"/>
@@ -4127,11 +4127,11 @@
         <v>363143</v>
       </c>
       <c r="V10" s="13">
-        <v>109571</v>
+        <v>112548</v>
       </c>
       <c r="W10" s="14">
         <f t="shared" si="2"/>
-        <v>-253572</v>
+        <v>-250595</v>
       </c>
       <c r="X10" s="12">
         <f t="shared" si="3"/>
@@ -4139,15 +4139,15 @@
       </c>
       <c r="Y10" s="13">
         <f t="shared" si="3"/>
-        <v>117717</v>
+        <v>120694</v>
       </c>
       <c r="Z10" s="14">
         <f t="shared" si="8"/>
-        <v>-405126</v>
+        <v>-402149</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="9"/>
-        <v>22.514789334465604</v>
+        <v>23.084176320616322</v>
       </c>
       <c r="AB10"/>
       <c r="AC10"/>
@@ -4378,11 +4378,11 @@
         <v>174056</v>
       </c>
       <c r="D11" s="6">
-        <v>70459</v>
+        <v>78348</v>
       </c>
       <c r="E11" s="14">
         <f t="shared" si="4"/>
-        <v>-103597</v>
+        <v>-95708</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -4450,15 +4450,15 @@
       </c>
       <c r="Y11" s="13">
         <f t="shared" si="3"/>
-        <v>84759</v>
+        <v>92648</v>
       </c>
       <c r="Z11" s="14">
         <f t="shared" si="8"/>
-        <v>-223084</v>
+        <v>-215195</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="9"/>
-        <v>27.533190619893904</v>
+        <v>30.095860552294511</v>
       </c>
     </row>
     <row r="12" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4566,11 +4566,11 @@
         <v>10884</v>
       </c>
       <c r="D13" s="6">
-        <v>1983</v>
+        <v>8855</v>
       </c>
       <c r="E13" s="14">
         <f t="shared" si="4"/>
-        <v>-8901</v>
+        <v>-2029</v>
       </c>
       <c r="F13" s="5">
         <v>1</v>
@@ -4638,15 +4638,15 @@
       </c>
       <c r="Y13" s="13">
         <f t="shared" si="3"/>
-        <v>3629</v>
+        <v>10501</v>
       </c>
       <c r="Z13" s="14">
         <f t="shared" si="8"/>
-        <v>-9565</v>
+        <v>-2693</v>
       </c>
       <c r="AA13" s="6">
         <f t="shared" si="9"/>
-        <v>27.50492648173412</v>
+        <v>79.589207215400933</v>
       </c>
     </row>
     <row r="14" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4754,21 +4754,21 @@
         <v>62500</v>
       </c>
       <c r="D15" s="6">
-        <v>31212</v>
+        <v>36888</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="4"/>
-        <v>-31288</v>
+        <v>-25612</v>
       </c>
       <c r="F15" s="5">
         <v>12000</v>
       </c>
       <c r="G15" s="6">
-        <v>3928</v>
+        <v>5156</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" si="0"/>
-        <v>-8072</v>
+        <v>-6844</v>
       </c>
       <c r="I15" s="5">
         <v>23000</v>
@@ -4826,15 +4826,15 @@
       </c>
       <c r="Y15" s="13">
         <f t="shared" si="3"/>
-        <v>35140</v>
+        <v>42044</v>
       </c>
       <c r="Z15" s="14">
         <f t="shared" si="8"/>
-        <v>-62360</v>
+        <v>-55456</v>
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="9"/>
-        <v>36.041025641025641</v>
+        <v>43.122051282051281</v>
       </c>
     </row>
     <row r="16" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4848,11 +4848,11 @@
         <v>285610</v>
       </c>
       <c r="D16" s="13">
-        <v>111485</v>
+        <v>112852</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="4"/>
-        <v>-174125</v>
+        <v>-172758</v>
       </c>
       <c r="F16" s="12">
         <v>0</v>
@@ -4920,15 +4920,15 @@
       </c>
       <c r="Y16" s="13">
         <f t="shared" si="3"/>
-        <v>116587</v>
+        <v>117954</v>
       </c>
       <c r="Z16" s="14">
         <f t="shared" si="8"/>
-        <v>-194325</v>
+        <v>-192958</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="9"/>
-        <v>37.49839182791272</v>
+        <v>37.938066076574721</v>
       </c>
       <c r="AB16"/>
       <c r="AC16"/>
@@ -5127,21 +5127,21 @@
         <v>69550</v>
       </c>
       <c r="D18" s="13">
-        <v>22945</v>
+        <v>23698</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="4"/>
-        <v>-46605</v>
+        <v>-45852</v>
       </c>
       <c r="F18" s="12">
         <v>12111</v>
       </c>
       <c r="G18" s="13">
-        <v>9239</v>
+        <v>9471</v>
       </c>
       <c r="H18" s="14">
         <f t="shared" si="0"/>
-        <v>-2872</v>
+        <v>-2640</v>
       </c>
       <c r="I18" s="12">
         <v>62003</v>
@@ -5187,11 +5187,11 @@
         <v>172069</v>
       </c>
       <c r="V18" s="29">
-        <v>41521</v>
+        <v>45306</v>
       </c>
       <c r="W18" s="14">
         <f t="shared" si="2"/>
-        <v>-130548</v>
+        <v>-126763</v>
       </c>
       <c r="X18" s="12">
         <f t="shared" si="3"/>
@@ -5199,15 +5199,15 @@
       </c>
       <c r="Y18" s="13">
         <f t="shared" si="3"/>
-        <v>80509</v>
+        <v>85279</v>
       </c>
       <c r="Z18" s="14">
         <f t="shared" si="8"/>
-        <v>-235224</v>
+        <v>-230454</v>
       </c>
       <c r="AA18" s="6">
         <f>Y18/X18*100</f>
-        <v>25.49907675155907</v>
+        <v>27.00984692762556</v>
       </c>
       <c r="AB18"/>
       <c r="AC18"/>
@@ -6856,11 +6856,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>301883</v>
+        <v>354585</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="4"/>
-        <v>-716470</v>
+        <v>-663768</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -6868,11 +6868,11 @@
       </c>
       <c r="G21" s="1">
         <f>SUM(G4:G20)</f>
-        <v>14031</v>
+        <v>15491</v>
       </c>
       <c r="H21" s="14">
         <f t="shared" si="0"/>
-        <v>-26201</v>
+        <v>-24741</v>
       </c>
       <c r="I21" s="2">
         <f>SUM(I4:I20)</f>
@@ -6880,11 +6880,11 @@
       </c>
       <c r="J21" s="1">
         <f>SUM(J4:J20)</f>
-        <v>10251</v>
+        <v>11290</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" si="5"/>
-        <v>-120341</v>
+        <v>-119302</v>
       </c>
       <c r="L21" s="2">
         <f>SUM(L4:L20)</f>
@@ -6904,11 +6904,11 @@
       </c>
       <c r="P21" s="1">
         <f>SUM(P4:P20)</f>
-        <v>3103250</v>
+        <v>3142858</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="7"/>
-        <v>-14265</v>
+        <v>25343</v>
       </c>
       <c r="R21" s="1">
         <f>SUM(R4:R20)</f>
@@ -6928,11 +6928,11 @@
       </c>
       <c r="V21" s="1">
         <f>SUM(V4:V20)</f>
-        <v>594201</v>
+        <v>631485</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="2"/>
-        <v>-706808</v>
+        <v>-669524</v>
       </c>
       <c r="X21" s="12">
         <f t="shared" si="13"/>
@@ -6940,15 +6940,15 @@
       </c>
       <c r="Y21" s="13">
         <f t="shared" si="13"/>
-        <v>4023616</v>
+        <v>4155709</v>
       </c>
       <c r="Z21" s="14">
         <f t="shared" si="8"/>
-        <v>-1584085</v>
+        <v>-1451992</v>
       </c>
       <c r="AA21" s="6">
         <f>Y21/X21*100</f>
-        <v>71.751614431653906</v>
+        <v>74.107178681602321</v>
       </c>
     </row>
     <row r="22" spans="1:1476" x14ac:dyDescent="0.25">
@@ -7848,7 +7848,7 @@
   <sheetData>
     <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -9145,11 +9145,11 @@
         <v>446600</v>
       </c>
       <c r="D16" s="6">
-        <v>244669</v>
+        <v>284479</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" si="2"/>
-        <v>-201931</v>
+        <v>-162121</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -9217,15 +9217,15 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="7"/>
-        <v>244669</v>
+        <v>284479</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="8"/>
-        <v>-201931</v>
+        <v>-162121</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="11"/>
-        <v>54.784818629646217</v>
+        <v>63.698835647111508</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -9612,11 +9612,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>246717</v>
+        <v>286527</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" ref="E21" si="20">D21-C21</f>
-        <v>-204884</v>
+        <v>-165074</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -9695,15 +9695,15 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="7"/>
-        <v>246844</v>
+        <v>286654</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="8"/>
-        <v>-204759</v>
+        <v>-164949</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="11"/>
-        <v>54.659512890746967</v>
+        <v>63.474777625480783</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">

--- a/data/fr/FR_Budget_Status.xlsx
+++ b/data/fr/FR_Budget_Status.xlsx
@@ -184,7 +184,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Actual.  Expenditure of Demand 16 GSU as on  17.08.2026  (Fig.in Thousand)</t>
+      <t>Actual.  Expenditure of Demand 16 GSU as on  27.08.2026  (Fig.in Thousand)</t>
     </r>
     <r>
       <rPr>
@@ -220,7 +220,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  17.08.2026  (Fig.in Thousand) </t>
+      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  27.08.2026  (Fig.in Thousand) </t>
     </r>
     <r>
       <rPr>
@@ -3213,11 +3213,11 @@
         <v>146190</v>
       </c>
       <c r="D4" s="13">
-        <v>76470</v>
+        <v>76481</v>
       </c>
       <c r="E4" s="14">
         <f>D4-C4</f>
-        <v>-69720</v>
+        <v>-69709</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
@@ -3285,15 +3285,15 @@
       </c>
       <c r="Y4" s="13">
         <f t="shared" si="3"/>
-        <v>77164</v>
+        <v>77175</v>
       </c>
       <c r="Z4" s="14">
         <f>Y4-X4</f>
-        <v>-83739</v>
+        <v>-83728</v>
       </c>
       <c r="AA4" s="6">
         <f>Y4/X4*100</f>
-        <v>47.956843564134914</v>
+        <v>47.96367998110663</v>
       </c>
       <c r="AB4"/>
       <c r="AC4"/>
@@ -3380,11 +3380,11 @@
         <v>4107</v>
       </c>
       <c r="D5" s="6">
-        <v>5001</v>
+        <v>7310</v>
       </c>
       <c r="E5" s="14">
         <f t="shared" ref="E5:E21" si="4">D5-C5</f>
-        <v>894</v>
+        <v>3203</v>
       </c>
       <c r="F5" s="5">
         <v>14120</v>
@@ -3452,15 +3452,15 @@
       </c>
       <c r="Y5" s="13">
         <f t="shared" si="3"/>
-        <v>8452</v>
+        <v>10761</v>
       </c>
       <c r="Z5" s="14">
         <f t="shared" ref="Z5:Z21" si="8">Y5-X5</f>
-        <v>-23775</v>
+        <v>-21466</v>
       </c>
       <c r="AA5" s="6">
         <f t="shared" ref="AA5:AA20" si="9">Y5/X5*100</f>
-        <v>26.226456077202347</v>
+        <v>33.391255779315479</v>
       </c>
     </row>
     <row r="6" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3514,11 +3514,11 @@
         <v>120318</v>
       </c>
       <c r="P6" s="8">
-        <v>55924</v>
+        <v>57023</v>
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="7"/>
-        <v>-64394</v>
+        <v>-63295</v>
       </c>
       <c r="R6" s="14">
         <v>0</v>
@@ -3546,15 +3546,15 @@
       </c>
       <c r="Y6" s="13">
         <f t="shared" si="3"/>
-        <v>55924</v>
+        <v>57023</v>
       </c>
       <c r="Z6" s="14">
         <f t="shared" si="8"/>
-        <v>-64394</v>
+        <v>-63295</v>
       </c>
       <c r="AA6" s="6">
         <f t="shared" si="9"/>
-        <v>46.480160906929967</v>
+        <v>47.393573696371284</v>
       </c>
     </row>
     <row r="7" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,11 +3608,11 @@
         <v>316420</v>
       </c>
       <c r="P7" s="8">
-        <v>230344</v>
+        <v>238818</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="7"/>
-        <v>-86076</v>
+        <v>-77602</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -3628,11 +3628,11 @@
         <v>191000</v>
       </c>
       <c r="V7" s="6">
-        <v>97525</v>
+        <v>98807</v>
       </c>
       <c r="W7" s="14">
         <f t="shared" si="2"/>
-        <v>-93475</v>
+        <v>-92193</v>
       </c>
       <c r="X7" s="12">
         <f t="shared" si="3"/>
@@ -3640,15 +3640,15 @@
       </c>
       <c r="Y7" s="13">
         <f t="shared" si="3"/>
-        <v>327869</v>
+        <v>337625</v>
       </c>
       <c r="Z7" s="14">
         <f t="shared" si="8"/>
-        <v>-179551</v>
+        <v>-169795</v>
       </c>
       <c r="AA7" s="6">
         <f t="shared" si="9"/>
-        <v>64.614914666351339</v>
+        <v>66.53758227897994</v>
       </c>
     </row>
     <row r="8" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3702,11 +3702,11 @@
         <v>2645397</v>
       </c>
       <c r="P8" s="8">
-        <v>2837402</v>
+        <v>2852005</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" si="7"/>
-        <v>192005</v>
+        <v>206608</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -3722,11 +3722,11 @@
         <v>317398</v>
       </c>
       <c r="V8" s="6">
-        <v>232941</v>
+        <v>258791</v>
       </c>
       <c r="W8" s="14">
         <f t="shared" si="2"/>
-        <v>-84457</v>
+        <v>-58607</v>
       </c>
       <c r="X8" s="12">
         <f t="shared" si="3"/>
@@ -3734,15 +3734,15 @@
       </c>
       <c r="Y8" s="13">
         <f t="shared" si="3"/>
-        <v>3070343</v>
+        <v>3110796</v>
       </c>
       <c r="Z8" s="14">
         <f t="shared" si="8"/>
-        <v>107548</v>
+        <v>148001</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="9"/>
-        <v>103.62995077283443</v>
+        <v>104.99531692202801</v>
       </c>
     </row>
     <row r="9" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3796,11 +3796,11 @@
         <v>35380</v>
       </c>
       <c r="P9" s="15">
-        <v>19188</v>
+        <v>27298</v>
       </c>
       <c r="Q9" s="14">
         <f t="shared" si="7"/>
-        <v>-16192</v>
+        <v>-8082</v>
       </c>
       <c r="R9" s="14">
         <v>0</v>
@@ -3828,15 +3828,15 @@
       </c>
       <c r="Y9" s="13">
         <f t="shared" si="3"/>
-        <v>142510</v>
+        <v>150620</v>
       </c>
       <c r="Z9" s="14">
         <f t="shared" si="8"/>
-        <v>10243</v>
+        <v>18353</v>
       </c>
       <c r="AA9" s="6">
         <f t="shared" si="9"/>
-        <v>107.74418411243923</v>
+        <v>113.87572107933195</v>
       </c>
       <c r="AB9"/>
       <c r="AC9"/>
@@ -4067,11 +4067,11 @@
         <v>159700</v>
       </c>
       <c r="D10" s="13">
-        <v>8146</v>
+        <v>8227</v>
       </c>
       <c r="E10" s="14">
         <f t="shared" si="4"/>
-        <v>-151554</v>
+        <v>-151473</v>
       </c>
       <c r="F10" s="12">
         <v>0</v>
@@ -4139,15 +4139,15 @@
       </c>
       <c r="Y10" s="13">
         <f t="shared" si="3"/>
-        <v>120694</v>
+        <v>120775</v>
       </c>
       <c r="Z10" s="14">
         <f t="shared" si="8"/>
-        <v>-402149</v>
+        <v>-402068</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="9"/>
-        <v>23.084176320616322</v>
+        <v>23.099668542946926</v>
       </c>
       <c r="AB10"/>
       <c r="AC10"/>
@@ -4438,11 +4438,11 @@
         <v>107957</v>
       </c>
       <c r="V11" s="6">
-        <v>14300</v>
+        <v>16570</v>
       </c>
       <c r="W11" s="14">
         <f t="shared" si="2"/>
-        <v>-93657</v>
+        <v>-91387</v>
       </c>
       <c r="X11" s="12">
         <f t="shared" si="3"/>
@@ -4450,15 +4450,15 @@
       </c>
       <c r="Y11" s="13">
         <f t="shared" si="3"/>
-        <v>92648</v>
+        <v>94918</v>
       </c>
       <c r="Z11" s="14">
         <f t="shared" si="8"/>
-        <v>-215195</v>
+        <v>-212925</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="9"/>
-        <v>30.095860552294511</v>
+        <v>30.833249416098468</v>
       </c>
     </row>
     <row r="12" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4754,11 +4754,11 @@
         <v>62500</v>
       </c>
       <c r="D15" s="6">
-        <v>36888</v>
+        <v>46863</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="4"/>
-        <v>-25612</v>
+        <v>-15637</v>
       </c>
       <c r="F15" s="5">
         <v>12000</v>
@@ -4826,15 +4826,15 @@
       </c>
       <c r="Y15" s="13">
         <f t="shared" si="3"/>
-        <v>42044</v>
+        <v>52019</v>
       </c>
       <c r="Z15" s="14">
         <f t="shared" si="8"/>
-        <v>-55456</v>
+        <v>-45481</v>
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="9"/>
-        <v>43.122051282051281</v>
+        <v>53.352820512820507</v>
       </c>
     </row>
     <row r="16" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4848,11 +4848,11 @@
         <v>285610</v>
       </c>
       <c r="D16" s="13">
-        <v>112852</v>
+        <v>120167</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="4"/>
-        <v>-172758</v>
+        <v>-165443</v>
       </c>
       <c r="F16" s="12">
         <v>0</v>
@@ -4920,15 +4920,15 @@
       </c>
       <c r="Y16" s="13">
         <f t="shared" si="3"/>
-        <v>117954</v>
+        <v>125269</v>
       </c>
       <c r="Z16" s="14">
         <f t="shared" si="8"/>
-        <v>-192958</v>
+        <v>-185643</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="9"/>
-        <v>37.938066076574721</v>
+        <v>40.290821840263483</v>
       </c>
       <c r="AB16"/>
       <c r="AC16"/>
@@ -5127,11 +5127,11 @@
         <v>69550</v>
       </c>
       <c r="D18" s="13">
-        <v>23698</v>
+        <v>29907</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="4"/>
-        <v>-45852</v>
+        <v>-39643</v>
       </c>
       <c r="F18" s="12">
         <v>12111</v>
@@ -5187,11 +5187,11 @@
         <v>172069</v>
       </c>
       <c r="V18" s="29">
-        <v>45306</v>
+        <v>52567</v>
       </c>
       <c r="W18" s="14">
         <f t="shared" si="2"/>
-        <v>-126763</v>
+        <v>-119502</v>
       </c>
       <c r="X18" s="12">
         <f t="shared" si="3"/>
@@ -5199,15 +5199,15 @@
       </c>
       <c r="Y18" s="13">
         <f t="shared" si="3"/>
-        <v>85279</v>
+        <v>98749</v>
       </c>
       <c r="Z18" s="14">
         <f t="shared" si="8"/>
-        <v>-230454</v>
+        <v>-216984</v>
       </c>
       <c r="AA18" s="6">
         <f>Y18/X18*100</f>
-        <v>27.00984692762556</v>
+        <v>31.276109877649787</v>
       </c>
       <c r="AB18"/>
       <c r="AC18"/>
@@ -6856,11 +6856,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>354585</v>
+        <v>380485</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="4"/>
-        <v>-663768</v>
+        <v>-637868</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -6904,11 +6904,11 @@
       </c>
       <c r="P21" s="1">
         <f>SUM(P4:P20)</f>
-        <v>3142858</v>
+        <v>3175144</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="7"/>
-        <v>25343</v>
+        <v>57629</v>
       </c>
       <c r="R21" s="1">
         <f>SUM(R4:R20)</f>
@@ -6928,11 +6928,11 @@
       </c>
       <c r="V21" s="1">
         <f>SUM(V4:V20)</f>
-        <v>631485</v>
+        <v>668148</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="2"/>
-        <v>-669524</v>
+        <v>-632861</v>
       </c>
       <c r="X21" s="12">
         <f t="shared" si="13"/>
@@ -6940,15 +6940,15 @@
       </c>
       <c r="Y21" s="13">
         <f t="shared" si="13"/>
-        <v>4155709</v>
+        <v>4250558</v>
       </c>
       <c r="Z21" s="14">
         <f t="shared" si="8"/>
-        <v>-1451992</v>
+        <v>-1357143</v>
       </c>
       <c r="AA21" s="6">
         <f>Y21/X21*100</f>
-        <v>74.107178681602321</v>
+        <v>75.798584838956288</v>
       </c>
     </row>
     <row r="22" spans="1:1476" x14ac:dyDescent="0.25">
@@ -9145,11 +9145,11 @@
         <v>446600</v>
       </c>
       <c r="D16" s="6">
-        <v>284479</v>
+        <v>302595</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" si="2"/>
-        <v>-162121</v>
+        <v>-144005</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -9217,15 +9217,15 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="7"/>
-        <v>284479</v>
+        <v>302595</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="8"/>
-        <v>-162121</v>
+        <v>-144005</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="11"/>
-        <v>63.698835647111508</v>
+        <v>67.755261979399904</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -9612,11 +9612,11 @@
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>286527</v>
+        <v>304643</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" ref="E21" si="20">D21-C21</f>
-        <v>-165074</v>
+        <v>-146958</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -9695,15 +9695,15 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="7"/>
-        <v>286654</v>
+        <v>304770</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="8"/>
-        <v>-164949</v>
+        <v>-146833</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="11"/>
-        <v>63.474777625480783</v>
+        <v>67.486265591681189</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">

--- a/data/fr/FR_Budget_Status.xlsx
+++ b/data/fr/FR_Budget_Status.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580F48C6-7F06-436C-A2E2-C1C44CFF7059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OPEN LINE FR" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,18 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'OPEN LINE FR'!$A$1:$Z$25</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -184,7 +196,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Actual.  Expenditure of Demand 16 GSU as on  27.08.2026  (Fig.in Thousand)</t>
+      <t>Actual.  Expenditure of Demand 16 GSU as on  05.09.2026  (Fig.in Thousand)</t>
     </r>
     <r>
       <rPr>
@@ -220,7 +232,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  27.08.2026  (Fig.in Thousand) </t>
+      <t xml:space="preserve">Actual.  Expenditure of Demand 16 upto as on  05.09.2026  (Fig.in Thousand) </t>
     </r>
     <r>
       <rPr>
@@ -238,7 +250,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1500,7 +1512,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1587,35 +1599,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2706,9 +2693,9 @@
     <cellStyle name="Hyperlink" xfId="1061" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1063" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="3"/>
-    <cellStyle name="Normal 3" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000025040000}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000026040000}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000027040000}"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2725,9 +2712,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2765,9 +2752,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2802,7 +2789,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2837,7 +2824,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3010,7 +2997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3044,89 +3031,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:244" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
     </row>
     <row r="2" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="49" t="s">
+      <c r="A2" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="46" t="s">
+      <c r="D2" s="39"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="46" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="46" t="s">
+      <c r="J2" s="39"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="48"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="46" t="s">
+      <c r="M2" s="39"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="46" t="s">
+      <c r="P2" s="39"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="48"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="46" t="s">
+      <c r="S2" s="39"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="43" t="s">
+      <c r="V2" s="39"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
     </row>
     <row r="3" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="41" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -3135,7 +3122,7 @@
       <c r="E3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -3144,7 +3131,7 @@
       <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="41" t="s">
+      <c r="I3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -3153,7 +3140,7 @@
       <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="M3" s="5" t="s">
@@ -3162,7 +3149,7 @@
       <c r="N3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="41" t="s">
+      <c r="O3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -3171,7 +3158,7 @@
       <c r="Q3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="41" t="s">
+      <c r="R3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="S3" s="2" t="s">
@@ -3180,7 +3167,7 @@
       <c r="T3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="U3" s="41" t="s">
+      <c r="U3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="V3" s="5" t="s">
@@ -3189,7 +3176,7 @@
       <c r="W3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="X3" s="41" t="s">
+      <c r="X3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="Y3" s="5" t="s">
@@ -3213,11 +3200,11 @@
         <v>146190</v>
       </c>
       <c r="D4" s="13">
-        <v>76481</v>
+        <v>77298</v>
       </c>
       <c r="E4" s="14">
         <f>D4-C4</f>
-        <v>-69709</v>
+        <v>-68892</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
@@ -3285,15 +3272,15 @@
       </c>
       <c r="Y4" s="13">
         <f t="shared" si="3"/>
-        <v>77175</v>
+        <v>77992</v>
       </c>
       <c r="Z4" s="14">
         <f>Y4-X4</f>
-        <v>-83728</v>
+        <v>-82911</v>
       </c>
       <c r="AA4" s="6">
         <f>Y4/X4*100</f>
-        <v>47.96367998110663</v>
+        <v>48.471439314369526</v>
       </c>
       <c r="AB4"/>
       <c r="AC4"/>
@@ -3380,11 +3367,11 @@
         <v>4107</v>
       </c>
       <c r="D5" s="6">
-        <v>7310</v>
+        <v>7690</v>
       </c>
       <c r="E5" s="14">
         <f t="shared" ref="E5:E21" si="4">D5-C5</f>
-        <v>3203</v>
+        <v>3583</v>
       </c>
       <c r="F5" s="5">
         <v>14120</v>
@@ -3400,11 +3387,11 @@
         <v>14000</v>
       </c>
       <c r="J5" s="6">
-        <v>2587</v>
+        <v>3247</v>
       </c>
       <c r="K5" s="14">
         <f t="shared" ref="K5:K21" si="5">J5-I5</f>
-        <v>-11413</v>
+        <v>-10753</v>
       </c>
       <c r="L5" s="14">
         <v>0</v>
@@ -3452,15 +3439,15 @@
       </c>
       <c r="Y5" s="13">
         <f t="shared" si="3"/>
-        <v>10761</v>
+        <v>11801</v>
       </c>
       <c r="Z5" s="14">
         <f t="shared" ref="Z5:Z21" si="8">Y5-X5</f>
-        <v>-21466</v>
+        <v>-20426</v>
       </c>
       <c r="AA5" s="6">
         <f t="shared" ref="AA5:AA20" si="9">Y5/X5*100</f>
-        <v>33.391255779315479</v>
+        <v>36.618363484035129</v>
       </c>
     </row>
     <row r="6" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3514,11 +3501,11 @@
         <v>120318</v>
       </c>
       <c r="P6" s="8">
-        <v>57023</v>
+        <v>57289</v>
       </c>
       <c r="Q6" s="14">
         <f t="shared" si="7"/>
-        <v>-63295</v>
+        <v>-63029</v>
       </c>
       <c r="R6" s="14">
         <v>0</v>
@@ -3546,15 +3533,15 @@
       </c>
       <c r="Y6" s="13">
         <f t="shared" si="3"/>
-        <v>57023</v>
+        <v>57289</v>
       </c>
       <c r="Z6" s="14">
         <f t="shared" si="8"/>
-        <v>-63295</v>
+        <v>-63029</v>
       </c>
       <c r="AA6" s="6">
         <f t="shared" si="9"/>
-        <v>47.393573696371284</v>
+        <v>47.614654498911221</v>
       </c>
     </row>
     <row r="7" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3608,11 +3595,11 @@
         <v>316420</v>
       </c>
       <c r="P7" s="8">
-        <v>238818</v>
+        <v>254179</v>
       </c>
       <c r="Q7" s="14">
         <f t="shared" si="7"/>
-        <v>-77602</v>
+        <v>-62241</v>
       </c>
       <c r="R7" s="7">
         <v>0</v>
@@ -3628,11 +3615,11 @@
         <v>191000</v>
       </c>
       <c r="V7" s="6">
-        <v>98807</v>
+        <v>109758</v>
       </c>
       <c r="W7" s="14">
         <f t="shared" si="2"/>
-        <v>-92193</v>
+        <v>-81242</v>
       </c>
       <c r="X7" s="12">
         <f t="shared" si="3"/>
@@ -3640,15 +3627,15 @@
       </c>
       <c r="Y7" s="13">
         <f t="shared" si="3"/>
-        <v>337625</v>
+        <v>363937</v>
       </c>
       <c r="Z7" s="14">
         <f t="shared" si="8"/>
-        <v>-169795</v>
+        <v>-143483</v>
       </c>
       <c r="AA7" s="6">
         <f t="shared" si="9"/>
-        <v>66.53758227897994</v>
+        <v>71.723030231366522</v>
       </c>
     </row>
     <row r="8" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3702,11 +3689,11 @@
         <v>2645397</v>
       </c>
       <c r="P8" s="8">
-        <v>2852005</v>
+        <v>3406763</v>
       </c>
       <c r="Q8" s="14">
         <f t="shared" si="7"/>
-        <v>206608</v>
+        <v>761366</v>
       </c>
       <c r="R8" s="7">
         <v>0</v>
@@ -3722,11 +3709,11 @@
         <v>317398</v>
       </c>
       <c r="V8" s="6">
-        <v>258791</v>
+        <v>285936</v>
       </c>
       <c r="W8" s="14">
         <f t="shared" si="2"/>
-        <v>-58607</v>
+        <v>-31462</v>
       </c>
       <c r="X8" s="12">
         <f t="shared" si="3"/>
@@ -3734,15 +3721,15 @@
       </c>
       <c r="Y8" s="13">
         <f t="shared" si="3"/>
-        <v>3110796</v>
+        <v>3692699</v>
       </c>
       <c r="Z8" s="14">
         <f t="shared" si="8"/>
-        <v>148001</v>
+        <v>729904</v>
       </c>
       <c r="AA8" s="6">
         <f t="shared" si="9"/>
-        <v>104.99531692202801</v>
+        <v>124.63565653377975</v>
       </c>
     </row>
     <row r="9" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3796,11 +3783,11 @@
         <v>35380</v>
       </c>
       <c r="P9" s="15">
-        <v>27298</v>
+        <v>27875</v>
       </c>
       <c r="Q9" s="14">
         <f t="shared" si="7"/>
-        <v>-8082</v>
+        <v>-7505</v>
       </c>
       <c r="R9" s="14">
         <v>0</v>
@@ -3828,15 +3815,15 @@
       </c>
       <c r="Y9" s="13">
         <f t="shared" si="3"/>
-        <v>150620</v>
+        <v>151197</v>
       </c>
       <c r="Z9" s="14">
         <f t="shared" si="8"/>
-        <v>18353</v>
+        <v>18930</v>
       </c>
       <c r="AA9" s="6">
         <f t="shared" si="9"/>
-        <v>113.87572107933195</v>
+        <v>114.31195989929461</v>
       </c>
       <c r="AB9"/>
       <c r="AC9"/>
@@ -4067,11 +4054,11 @@
         <v>159700</v>
       </c>
       <c r="D10" s="13">
-        <v>8227</v>
+        <v>10447</v>
       </c>
       <c r="E10" s="14">
         <f t="shared" si="4"/>
-        <v>-151473</v>
+        <v>-149253</v>
       </c>
       <c r="F10" s="12">
         <v>0</v>
@@ -4127,11 +4114,11 @@
         <v>363143</v>
       </c>
       <c r="V10" s="13">
-        <v>112548</v>
+        <v>112591</v>
       </c>
       <c r="W10" s="14">
         <f t="shared" si="2"/>
-        <v>-250595</v>
+        <v>-250552</v>
       </c>
       <c r="X10" s="12">
         <f t="shared" si="3"/>
@@ -4139,15 +4126,15 @@
       </c>
       <c r="Y10" s="13">
         <f t="shared" si="3"/>
-        <v>120775</v>
+        <v>123038</v>
       </c>
       <c r="Z10" s="14">
         <f t="shared" si="8"/>
-        <v>-402068</v>
+        <v>-399805</v>
       </c>
       <c r="AA10" s="6">
         <f t="shared" si="9"/>
-        <v>23.099668542946926</v>
+        <v>23.532494458183432</v>
       </c>
       <c r="AB10"/>
       <c r="AC10"/>
@@ -4378,11 +4365,11 @@
         <v>174056</v>
       </c>
       <c r="D11" s="6">
-        <v>78348</v>
+        <v>78354</v>
       </c>
       <c r="E11" s="14">
         <f t="shared" si="4"/>
-        <v>-95708</v>
+        <v>-95702</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -4450,15 +4437,15 @@
       </c>
       <c r="Y11" s="13">
         <f t="shared" si="3"/>
-        <v>94918</v>
+        <v>94924</v>
       </c>
       <c r="Z11" s="14">
         <f t="shared" si="8"/>
-        <v>-212925</v>
+        <v>-212919</v>
       </c>
       <c r="AA11" s="6">
         <f t="shared" si="9"/>
-        <v>30.833249416098468</v>
+        <v>30.835198461553453</v>
       </c>
     </row>
     <row r="12" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4478,7 +4465,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" s="6">
@@ -4566,11 +4553,11 @@
         <v>10884</v>
       </c>
       <c r="D13" s="6">
-        <v>8855</v>
+        <v>22627</v>
       </c>
       <c r="E13" s="14">
         <f t="shared" si="4"/>
-        <v>-2029</v>
+        <v>11743</v>
       </c>
       <c r="F13" s="5">
         <v>1</v>
@@ -4638,15 +4625,15 @@
       </c>
       <c r="Y13" s="13">
         <f t="shared" si="3"/>
-        <v>10501</v>
+        <v>24273</v>
       </c>
       <c r="Z13" s="14">
         <f t="shared" si="8"/>
-        <v>-2693</v>
+        <v>11079</v>
       </c>
       <c r="AA13" s="6">
         <f t="shared" si="9"/>
-        <v>79.589207215400933</v>
+        <v>183.9699863574352</v>
       </c>
     </row>
     <row r="14" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4660,11 +4647,11 @@
         <v>35702</v>
       </c>
       <c r="D14" s="6">
-        <v>4327</v>
+        <v>5129</v>
       </c>
       <c r="E14" s="14">
         <f t="shared" si="4"/>
-        <v>-31375</v>
+        <v>-30573</v>
       </c>
       <c r="F14" s="5">
         <v>2000</v>
@@ -4732,19 +4719,19 @@
       </c>
       <c r="Y14" s="13">
         <f t="shared" si="3"/>
-        <v>4327</v>
+        <v>5129</v>
       </c>
       <c r="Z14" s="14">
         <f t="shared" si="8"/>
-        <v>-49375</v>
+        <v>-48573</v>
       </c>
       <c r="AA14" s="6">
         <f t="shared" si="9"/>
-        <v>8.0574280287512572</v>
+        <v>9.5508547167703259</v>
       </c>
     </row>
     <row r="15" spans="1:244" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40">
+      <c r="A15" s="1">
         <v>5100</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -4754,11 +4741,11 @@
         <v>62500</v>
       </c>
       <c r="D15" s="6">
-        <v>46863</v>
+        <v>50145</v>
       </c>
       <c r="E15" s="14">
         <f t="shared" si="4"/>
-        <v>-15637</v>
+        <v>-12355</v>
       </c>
       <c r="F15" s="5">
         <v>12000</v>
@@ -4774,11 +4761,11 @@
         <v>23000</v>
       </c>
       <c r="J15" s="6">
-        <v>0</v>
+        <v>4551</v>
       </c>
       <c r="K15" s="14">
         <f t="shared" si="5"/>
-        <v>-23000</v>
+        <v>-18449</v>
       </c>
       <c r="L15" s="7">
         <v>0</v>
@@ -4826,15 +4813,15 @@
       </c>
       <c r="Y15" s="13">
         <f t="shared" si="3"/>
-        <v>52019</v>
+        <v>59852</v>
       </c>
       <c r="Z15" s="14">
         <f t="shared" si="8"/>
-        <v>-45481</v>
+        <v>-37648</v>
       </c>
       <c r="AA15" s="6">
         <f t="shared" si="9"/>
-        <v>53.352820512820507</v>
+        <v>61.38666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:244" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4848,11 +4835,11 @@
         <v>285610</v>
       </c>
       <c r="D16" s="13">
-        <v>120167</v>
+        <v>125946</v>
       </c>
       <c r="E16" s="14">
         <f t="shared" si="4"/>
-        <v>-165443</v>
+        <v>-159664</v>
       </c>
       <c r="F16" s="12">
         <v>0</v>
@@ -4920,19 +4907,19 @@
       </c>
       <c r="Y16" s="13">
         <f t="shared" si="3"/>
-        <v>125269</v>
+        <v>131048</v>
       </c>
       <c r="Z16" s="14">
         <f t="shared" si="8"/>
-        <v>-185643</v>
+        <v>-179864</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="9"/>
-        <v>40.290821840263483</v>
+        <v>42.149547138740225</v>
       </c>
       <c r="AB16"/>
       <c r="AC16"/>
-      <c r="AD16" s="31"/>
+      <c r="AD16"/>
       <c r="AE16"/>
       <c r="AF16"/>
       <c r="AG16"/>
@@ -5127,11 +5114,11 @@
         <v>69550</v>
       </c>
       <c r="D18" s="13">
-        <v>29907</v>
+        <v>31206</v>
       </c>
       <c r="E18" s="14">
         <f t="shared" si="4"/>
-        <v>-39643</v>
+        <v>-38344</v>
       </c>
       <c r="F18" s="12">
         <v>12111</v>
@@ -5147,11 +5134,11 @@
         <v>62003</v>
       </c>
       <c r="J18" s="13">
-        <v>6804</v>
+        <v>8762</v>
       </c>
       <c r="K18" s="14">
         <f t="shared" si="5"/>
-        <v>-55199</v>
+        <v>-53241</v>
       </c>
       <c r="L18" s="14">
         <v>0</v>
@@ -5187,11 +5174,11 @@
         <v>172069</v>
       </c>
       <c r="V18" s="29">
-        <v>52567</v>
+        <v>53936</v>
       </c>
       <c r="W18" s="14">
         <f t="shared" si="2"/>
-        <v>-119502</v>
+        <v>-118133</v>
       </c>
       <c r="X18" s="12">
         <f t="shared" si="3"/>
@@ -5199,15 +5186,15 @@
       </c>
       <c r="Y18" s="13">
         <f t="shared" si="3"/>
-        <v>98749</v>
+        <v>103375</v>
       </c>
       <c r="Z18" s="14">
         <f t="shared" si="8"/>
-        <v>-216984</v>
+        <v>-212358</v>
       </c>
       <c r="AA18" s="6">
         <f>Y18/X18*100</f>
-        <v>31.276109877649787</v>
+        <v>32.741271897457665</v>
       </c>
       <c r="AB18"/>
       <c r="AC18"/>
@@ -6758,7 +6745,7 @@
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="2">
         <v>6000</v>
       </c>
       <c r="D20" s="6">
@@ -6846,21 +6833,21 @@
       </c>
     </row>
     <row r="21" spans="1:1476" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="33">
+      <c r="B21" s="38"/>
+      <c r="C21" s="2">
         <f>SUM(C4:C20)</f>
         <v>1018353</v>
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>380485</v>
+        <v>408842</v>
       </c>
       <c r="E21" s="14">
         <f t="shared" si="4"/>
-        <v>-637868</v>
+        <v>-609511</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -6880,11 +6867,11 @@
       </c>
       <c r="J21" s="1">
         <f>SUM(J4:J20)</f>
-        <v>11290</v>
+        <v>18459</v>
       </c>
       <c r="K21" s="14">
         <f t="shared" si="5"/>
-        <v>-119302</v>
+        <v>-112133</v>
       </c>
       <c r="L21" s="2">
         <f>SUM(L4:L20)</f>
@@ -6904,11 +6891,11 @@
       </c>
       <c r="P21" s="1">
         <f>SUM(P4:P20)</f>
-        <v>3175144</v>
+        <v>3746106</v>
       </c>
       <c r="Q21" s="14">
         <f t="shared" si="7"/>
-        <v>57629</v>
+        <v>628591</v>
       </c>
       <c r="R21" s="1">
         <f>SUM(R4:R20)</f>
@@ -6928,11 +6915,11 @@
       </c>
       <c r="V21" s="1">
         <f>SUM(V4:V20)</f>
-        <v>668148</v>
+        <v>707656</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="2"/>
-        <v>-632861</v>
+        <v>-593353</v>
       </c>
       <c r="X21" s="12">
         <f t="shared" si="13"/>
@@ -6940,15 +6927,15 @@
       </c>
       <c r="Y21" s="13">
         <f t="shared" si="13"/>
-        <v>4250558</v>
+        <v>4896554</v>
       </c>
       <c r="Z21" s="14">
         <f t="shared" si="8"/>
-        <v>-1357143</v>
+        <v>-711147</v>
       </c>
       <c r="AA21" s="6">
         <f>Y21/X21*100</f>
-        <v>75.798584838956288</v>
+        <v>87.318385912515666</v>
       </c>
     </row>
     <row r="22" spans="1:1476" x14ac:dyDescent="0.25">
@@ -6983,37 +6970,37 @@
       <c r="B23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="37"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="31"/>
     </row>
     <row r="24" spans="1:1476" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="37"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="31"/>
       <c r="W24" t="s">
         <v>27</v>
       </c>
@@ -7022,35 +7009,35 @@
       <c r="B25" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="38"/>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="38"/>
-      <c r="P25" s="37"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="31"/>
       <c r="W25" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:1476" x14ac:dyDescent="0.25">
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="39"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="39"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
     </row>
     <row r="32" spans="1:1476" x14ac:dyDescent="0.25">
       <c r="A32" s="17"/>
@@ -7833,7 +7820,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7847,89 +7834,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="42"/>
+      <c r="X1" s="42"/>
+      <c r="Y1" s="42"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
     </row>
     <row r="2" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="50" t="s">
+      <c r="A2" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50" t="s">
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50" t="s">
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50" t="s">
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50" t="s">
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50" t="s">
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50" t="s">
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="50"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="43" t="s">
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
     </row>
     <row r="3" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="42" t="s">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -7938,7 +7925,7 @@
       <c r="E3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -7956,7 +7943,7 @@
       <c r="K3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M3" s="5" t="s">
@@ -7965,7 +7952,7 @@
       <c r="N3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="42" t="s">
+      <c r="O3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="P3" s="5" t="s">
@@ -7974,7 +7961,7 @@
       <c r="Q3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="42" t="s">
+      <c r="R3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="S3" s="2" t="s">
@@ -7983,7 +7970,7 @@
       <c r="T3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="U3" s="42" t="s">
+      <c r="U3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="V3" s="5" t="s">
@@ -7992,7 +7979,7 @@
       <c r="W3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="X3" s="42" t="s">
+      <c r="X3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="Y3" s="5" t="s">
@@ -8098,7 +8085,7 @@
         <f t="shared" ref="AA4:AA6" si="1">Y4/X4*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB4" s="34"/>
+      <c r="AB4" s="30"/>
     </row>
     <row r="5" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -8193,14 +8180,14 @@
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="37"/>
-      <c r="AD5" s="37"/>
-      <c r="AE5" s="37"/>
-      <c r="AF5" s="37"/>
-      <c r="AG5" s="37"/>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="37"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="31"/>
+      <c r="AI5" s="31"/>
     </row>
     <row r="6" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -8585,10 +8572,10 @@
       <c r="B10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="36">
-        <v>0</v>
-      </c>
-      <c r="D10" s="35">
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="7">
@@ -8671,7 +8658,7 @@
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB10" s="34"/>
+      <c r="AB10" s="30"/>
     </row>
     <row r="11" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -8766,7 +8753,7 @@
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB11" s="37"/>
+      <c r="AB11" s="31"/>
     </row>
     <row r="12" spans="1:35" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -8956,7 +8943,7 @@
       <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="2">
         <v>5001</v>
       </c>
       <c r="D14" s="6">
@@ -9145,11 +9132,11 @@
         <v>446600</v>
       </c>
       <c r="D16" s="6">
-        <v>302595</v>
+        <v>317088</v>
       </c>
       <c r="E16" s="7">
         <f t="shared" si="2"/>
-        <v>-144005</v>
+        <v>-129512</v>
       </c>
       <c r="F16" s="5">
         <v>0</v>
@@ -9217,15 +9204,15 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="7"/>
-        <v>302595</v>
+        <v>317088</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="8"/>
-        <v>-144005</v>
+        <v>-129512</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="11"/>
-        <v>67.755261979399904</v>
+        <v>71.000447828034027</v>
       </c>
     </row>
     <row r="17" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -9602,21 +9589,21 @@
       </c>
     </row>
     <row r="21" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="47"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="2">
         <f>SUM(C4:C20)</f>
         <v>451601</v>
       </c>
       <c r="D21" s="1">
         <f>SUM(D4:D20)</f>
-        <v>304643</v>
+        <v>319136</v>
       </c>
       <c r="E21" s="7">
         <f t="shared" ref="E21" si="20">D21-C21</f>
-        <v>-146958</v>
+        <v>-132465</v>
       </c>
       <c r="F21" s="2">
         <f>SUM(F4:F20)</f>
@@ -9695,15 +9682,15 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="7"/>
-        <v>304770</v>
+        <v>319263</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="8"/>
-        <v>-146833</v>
+        <v>-132340</v>
       </c>
       <c r="AA21" s="6">
         <f t="shared" si="11"/>
-        <v>67.486265591681189</v>
+        <v>70.695500251326933</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.25">
@@ -9761,32 +9748,32 @@
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="45"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
-      <c r="P36" s="45"/>
-      <c r="Q36" s="45"/>
-      <c r="R36" s="45"/>
-      <c r="S36" s="45"/>
-      <c r="T36" s="45"/>
-      <c r="U36" s="45"/>
-      <c r="V36" s="45"/>
-      <c r="W36" s="45"/>
-      <c r="X36" s="45"/>
-      <c r="Y36" s="45"/>
-      <c r="Z36" s="45"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
+      <c r="Z36" s="36"/>
       <c r="AA36" t="s">
         <v>36</v>
       </c>
